--- a/Codelist Excel Files and Conversion Templates to XML/soundingPurpose.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/soundingPurpose.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Draft Excel Codelists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01621058-B1E3-074C-AD65-879A3451DE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4694E0CE-5B08-584C-8215-73767BE3555D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19860" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -773,9 +773,6 @@
     <t>Seismic Cone Penetrometer</t>
   </si>
   <si>
-    <t>//diggs:Sounding/diggs:SoundingPurpose</t>
-  </si>
-  <si>
     <t>Pressuremeter</t>
   </si>
   <si>
@@ -804,6 +801,9 @@
   </si>
   <si>
     <t>Sounding is created for the purpose of driven pile installation</t>
+  </si>
+  <si>
+    <t>//diggs:Sounding/diggs:soundingPurpose</t>
   </si>
 </sst>
 </file>
@@ -962,7 +962,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -995,23 +995,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1029,6 +1013,30 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1064,12 +1072,6 @@
       <font>
         <color auto="1"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1085,80 +1087,6 @@
           <color rgb="FFFFFFFF"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1227,6 +1155,62 @@
       </font>
       <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1241,50 +1225,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="7">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2829,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D7" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D7" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="19">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1812,1,FALSE)),"Not listed","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ConditionalElement"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1618,7 +1602,7 @@
         <v>234</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1669,7 @@
         <v>236</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>4</v>
@@ -1708,7 +1692,7 @@
         <v>239</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>4</v>
@@ -1731,7 +1715,7 @@
         <v>241</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>4</v>
@@ -1751,10 +1735,10 @@
         <v>242</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>4</v>
@@ -1777,7 +1761,7 @@
         <v>244</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>4</v>
@@ -1789,23 +1773,23 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="str">
+      <c r="A7" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2834,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1851,7 +1835,7 @@
         <v>235</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1863,7 +1847,7 @@
         <v>238</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1875,7 +1859,7 @@
         <v>240</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1887,7 +1871,7 @@
         <v>242</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1899,19 +1883,19 @@
         <v>243</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="str">
+      <c r="A7" t="str">
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1812,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>253</v>
+      <c r="B7" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
